--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484224_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484224_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>P. DÍAZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0898</v>
+        <v>2.1817</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6249</v>
+        <v>2.7422</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5351</v>
+        <v>-0.5605</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8861</v>
+        <v>1.8101</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2842</v>
+        <v>1.4193</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1703</v>
+        <v>0.3908</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0224</v>
+        <v>2.434</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9864</v>
+        <v>2.3126</v>
       </c>
       <c r="L2" t="n">
-        <v>3.0359</v>
+        <v>0.1214</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.1362</v>
+        <v>-0.6239</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2707</v>
+        <v>-0.8933</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1344</v>
+        <v>0.2694</v>
       </c>
       <c r="P2" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-2.1488</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.399</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7513</v>
+        <v>-0.3831</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3523</v>
+        <v>0.3053</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. DÍAZ JIMÉNEZ</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3529</v>
+        <v>2.0787</v>
       </c>
       <c r="E3" t="n">
-        <v>2.641</v>
+        <v>2.6138</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2881</v>
+        <v>-0.5351</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8101</v>
+        <v>2.8861</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4193</v>
+        <v>-0.2842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3908</v>
+        <v>3.1703</v>
       </c>
       <c r="J3" t="n">
-        <v>2.434</v>
+        <v>5.0224</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3126</v>
+        <v>1.9864</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1214</v>
+        <v>3.0359</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6239</v>
+        <v>-2.1362</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8933</v>
+        <v>-2.2707</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2694</v>
+        <v>0.1344</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0935</v>
+        <v>-0.6121</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4842</v>
+        <v>-0.2598</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5777</v>
+        <v>-0.3523</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.3447</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3256</v>
+        <v>0.6289</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3931</v>
+        <v>-0.2842</v>
       </c>
       <c r="G4" t="n">
         <v>0.0667</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2672</v>
+        <v>-0.8549</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0894</v>
+        <v>-0.7861</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1778</v>
+        <v>-0.0689</v>
       </c>
       <c r="V4" t="n">
         <v>1.3283</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0949</v>
+        <v>-0.0255</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3652</v>
+        <v>-1.0404</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2703</v>
+        <v>1.0149</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2626</v>
+        <v>-2.139</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8716</v>
+        <v>-1.3579</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.391</v>
+        <v>-0.7811</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2525</v>
+        <v>-1.1056</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2663</v>
+        <v>-0.3249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0138</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0101</v>
+        <v>-1.0334</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3948</v>
+        <v>-1.033</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4049</v>
+        <v>-0.0004</v>
       </c>
       <c r="P5" t="n">
         <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0044</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1127</v>
+        <v>-0.7861</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1083</v>
+        <v>-0.1005</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.0617</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4043</v>
+        <v>-1.3047</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8242</v>
+        <v>1.243</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.139</v>
+        <v>-1.2626</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3579</v>
+        <v>-0.8716</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7811</v>
+        <v>-0.391</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1056</v>
+        <v>-1.2525</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3249</v>
+        <v>-1.2663</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0.0138</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0334</v>
+        <v>-0.0101</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.033</v>
+        <v>0.3948</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004</v>
+        <v>-0.4049</v>
       </c>
       <c r="P6" t="n">
         <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4411</v>
+        <v>0.0289</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1499</v>
+        <v>-0.0522</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2911</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0015</v>
+        <v>-1.0499</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6611</v>
+        <v>-1.6006</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6596</v>
+        <v>0.5507</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0032</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.197</v>
+        <v>0.1486</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0083</v>
+        <v>0.0689</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1887</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6093</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5752</v>
+        <v>-1.3536</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1859</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3893</v>
+        <v>-0.471</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8742</v>
@@ -1078,13 +1078,13 @@
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5057</v>
+        <v>-0.284</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5447</v>
+        <v>-0.2414</v>
       </c>
       <c r="U8" t="n">
-        <v>0.039</v>
+        <v>-0.0427</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.361</v>
+        <v>-2.6038</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0492</v>
+        <v>-3.292</v>
       </c>
       <c r="F9" t="n">
         <v>0.6882</v>
@@ -1156,10 +1156,10 @@
         <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3631</v>
+        <v>-0.606</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4153</v>
+        <v>-0.6581</v>
       </c>
       <c r="U9" t="n">
         <v>0.0522</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3522</v>
+        <v>-2.7394</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.02</v>
+        <v>-2.3528</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3322</v>
+        <v>-0.3867</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1597</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.892</v>
+        <v>-0.2792</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.2406</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0159</v>
+        <v>-0.0386</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9928</v>
+        <v>-7.0511</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1647</v>
+        <v>-2.4681</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8281</v>
+        <v>-4.583</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2061</v>
@@ -1312,13 +1312,13 @@
         <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5215</v>
+        <v>-0.5798</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2588</v>
+        <v>-0.0446</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7803</v>
+        <v>-0.5352</v>
       </c>
       <c r="V11" t="n">
         <v>-4.2652</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.5826</v>
+        <v>-10.2799</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.258900000000001</v>
+        <v>-6.956300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3236</v>
+        <v>-3.3237</v>
       </c>
       <c r="G12" t="n">
         <v>-7.8565</v>
@@ -1360,10 +1360,10 @@
         <v>-7.1872</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6691999999999991</v>
+        <v>-0.6691999999999996</v>
       </c>
       <c r="J12" t="n">
-        <v>5.2457</v>
+        <v>5.245700000000001</v>
       </c>
       <c r="K12" t="n">
         <v>6.586100000000001</v>
@@ -1390,13 +1390,13 @@
         <v>16.6042</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.305499999999999</v>
+        <v>-4.0028</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6856</v>
+        <v>-3.3831</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6197</v>
+        <v>-0.6199</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3276</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.8317</v>
+        <v>7.2828</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3409</v>
+        <v>5.8465</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4908</v>
+        <v>1.4364</v>
       </c>
       <c r="G13" t="n">
         <v>5.4644</v>
@@ -1468,13 +1468,13 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4808</v>
+        <v>0.9319</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.652</v>
+        <v>-0.1464</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1328</v>
+        <v>1.0783</v>
       </c>
       <c r="V13" t="n">
         <v>0.8865</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7403</v>
+        <v>3.141</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2095</v>
+        <v>2.3107</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5308</v>
+        <v>0.8303</v>
       </c>
       <c r="G14" t="n">
         <v>2.5619</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0649</v>
+        <v>0.4656</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0246</v>
+        <v>0.0765</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0895</v>
+        <v>0.3891</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2772</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SEKOU MOUSSA</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9514</v>
+        <v>2.0952</v>
       </c>
       <c r="E15" t="n">
-        <v>0.862</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0894</v>
+        <v>1.2298</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3032</v>
+        <v>-0.6936</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5889</v>
+        <v>-2.3654</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7144</v>
+        <v>1.6717</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8437</v>
+        <v>0.6901</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8032</v>
+        <v>-1.118</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0405</v>
+        <v>1.8081</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4595</v>
+        <v>-1.3838</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2144</v>
+        <v>-1.2474</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.1364</v>
       </c>
       <c r="P15" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0035</v>
+        <v>0.2111</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8545</v>
+        <v>-0.2537</v>
       </c>
       <c r="U15" t="n">
-        <v>0.149</v>
+        <v>0.4648</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5507</v>
+        <v>2.3824</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6642</v>
+        <v>2.3824</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6397</v>
+        <v>1.5229</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0152</v>
+        <v>-0.914</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6548</v>
+        <v>2.4369</v>
       </c>
       <c r="G16" t="n">
         <v>0.2722</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4697</v>
+        <v>1.3529</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1594</v>
+        <v>-0.0583</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6291</v>
+        <v>1.4112</v>
       </c>
       <c r="V16" t="n">
         <v>2.4373</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4262</v>
+        <v>1.1817</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3599</v>
+        <v>0.0282</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0664</v>
+        <v>1.1534</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6936</v>
+        <v>0.3466</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3654</v>
+        <v>-0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6717</v>
+        <v>0.4045</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6901</v>
+        <v>0.0819</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.118</v>
+        <v>0.0819</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8081</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3838</v>
+        <v>0.2648</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2474</v>
+        <v>-0.1397</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1364</v>
+        <v>0.4045</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4579</v>
+        <v>0.4443</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7592</v>
+        <v>0.1417</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3014</v>
+        <v>0.3026</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>T. SEKOU MOUSSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9794</v>
+        <v>0.6212</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.174</v>
+        <v>-0.2503</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1534</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3466</v>
+        <v>1.3032</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0578</v>
+        <v>0.5889</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4045</v>
+        <v>0.7144</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0819</v>
+        <v>0.8437</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0819</v>
+        <v>0.8032</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2648</v>
+        <v>0.4595</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1397</v>
+        <v>-0.2144</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4045</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2421</v>
+        <v>0.6734</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0605</v>
+        <v>0.7422</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3026</v>
+        <v>-0.0689</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.5507</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0798</v>
+        <v>-1.9593</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4718</v>
+        <v>-2.2696</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3921</v>
+        <v>0.3104</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1421</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3517</v>
+        <v>-0.2311</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2283</v>
+        <v>-0.0261</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1233</v>
+        <v>-0.205</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9064</v>
+        <v>-3.303</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7876</v>
+        <v>-2.2932</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1187</v>
+        <v>-1.0098</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2562</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.854</v>
+        <v>0.4574</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6495</v>
+        <v>0.1439</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2045</v>
+        <v>0.3135</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5507</v>
@@ -2050,10 +2050,10 @@
         <v>10.5825</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3237</v>
+        <v>3.323699999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>7.259</v>
+        <v>7.258900000000001</v>
       </c>
       <c r="G21" t="n">
         <v>7.856400000000001</v>
@@ -2062,7 +2062,7 @@
         <v>7.1873</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6690999999999998</v>
+        <v>0.6691</v>
       </c>
       <c r="J21" t="n">
         <v>13.1021</v>
@@ -2071,10 +2071,10 @@
         <v>13.7732</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6710999999999998</v>
+        <v>-0.6711</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.245699999999999</v>
+        <v>-5.2457</v>
       </c>
       <c r="N21" t="n">
         <v>-6.5861</v>
@@ -2092,10 +2092,10 @@
         <v>12.6973</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3054</v>
+        <v>4.3055</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6199999999999999</v>
+        <v>0.6197999999999998</v>
       </c>
       <c r="U21" t="n">
         <v>3.6856</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484224_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484224_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. DÍAZ JIMÉNEZ</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1817</v>
+        <v>2.0787</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7422</v>
+        <v>2.6138</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5605</v>
+        <v>-0.5351</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8101</v>
+        <v>2.8861</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4193</v>
+        <v>-0.2842</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3908</v>
+        <v>3.1703</v>
       </c>
       <c r="J2" t="n">
-        <v>2.434</v>
+        <v>5.0224</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3126</v>
+        <v>1.9864</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1214</v>
+        <v>3.0359</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6239</v>
+        <v>-2.1362</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8933</v>
+        <v>-2.2707</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2694</v>
+        <v>0.1344</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.6121</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3831</v>
+        <v>-0.2598</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3053</v>
+        <v>-0.3523</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>P. DIAZ JIMENEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +653,72 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0787</v>
+        <v>1.8747</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6138</v>
+        <v>2.4352</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5351</v>
+        <v>-0.5605</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8861</v>
+        <v>1.5032</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2842</v>
+        <v>1.1123</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1703</v>
+        <v>0.3908</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0224</v>
+        <v>2.127</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9864</v>
+        <v>2.0056</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0359</v>
+        <v>0.1214</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1362</v>
+        <v>-0.6239</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2707</v>
+        <v>-0.8933</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1344</v>
+        <v>0.2694</v>
       </c>
       <c r="P3" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.1488</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6121</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2598</v>
+        <v>-0.3831</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3523</v>
+        <v>0.3053</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3447</v>
+        <v>1.221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6289</v>
+        <v>1.221</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2842</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0667</v>
+        <v>1.221</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7012</v>
+        <v>0.614</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7679</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0679</v>
+        <v>1.221</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8391</v>
+        <v>0.614</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2288</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0012</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5403</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5391</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8549</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7861</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0689</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3283</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1675</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>P. DÍAZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0255</v>
+        <v>0.307</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0404</v>
+        <v>0.307</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0149</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.139</v>
+        <v>0.307</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3579</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7811</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1056</v>
+        <v>0.307</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3249</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7806999999999999</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0334</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.033</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8866000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7861</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1005</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0617</v>
+        <v>-0.0255</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3047</v>
+        <v>-1.0404</v>
       </c>
       <c r="F6" t="n">
-        <v>1.243</v>
+        <v>1.0149</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2626</v>
+        <v>-2.139</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8716</v>
+        <v>-1.3579</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.391</v>
+        <v>-0.7811</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2525</v>
+        <v>-1.1056</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2663</v>
+        <v>-0.3249</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0138</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0101</v>
+        <v>-1.0334</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3948</v>
+        <v>-1.033</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4049</v>
+        <v>-0.0004</v>
       </c>
       <c r="P6" t="n">
         <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0289</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0522</v>
+        <v>-0.7861</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08110000000000001</v>
+        <v>-0.1005</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0499</v>
+        <v>-0.0617</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6006</v>
+        <v>-1.3047</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5507</v>
+        <v>1.243</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0032</v>
+        <v>-1.2626</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0353</v>
+        <v>-0.8716</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0385</v>
+        <v>-0.391</v>
       </c>
       <c r="J7" t="n">
-        <v>0.616</v>
+        <v>-1.2525</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2497</v>
+        <v>-1.2663</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0138</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6192</v>
+        <v>-0.0101</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2144</v>
+        <v>0.3948</v>
       </c>
       <c r="O7" t="n">
         <v>-0.4049</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1486</v>
+        <v>0.0289</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0689</v>
+        <v>-0.0522</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3536</v>
+        <v>-0.8762</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.5921</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.471</v>
+        <v>-0.2842</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8742</v>
+        <v>-1.1543</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3528</v>
+        <v>-2.3152</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.227</v>
+        <v>1.1609</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3122</v>
+        <v>0.8469</v>
       </c>
       <c r="K8" t="n">
-        <v>2.539</v>
+        <v>0.2251</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2268</v>
+        <v>0.6218</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1864</v>
+        <v>-2.0012</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.1862</v>
+        <v>-2.5403</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>0.5391</v>
       </c>
       <c r="P8" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.284</v>
+        <v>-0.8549</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2414</v>
+        <v>-0.7861</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0427</v>
+        <v>-0.0689</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1675</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6038</v>
+        <v>-1.0499</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.292</v>
+        <v>-1.6006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6882</v>
+        <v>0.5507</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9746</v>
+        <v>-0.0032</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.9317</v>
+        <v>1.0353</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9572000000000001</v>
+        <v>-1.0385</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6572</v>
+        <v>0.616</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9404</v>
+        <v>1.2497</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2833</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3174</v>
+        <v>-0.6192</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9913</v>
+        <v>-0.2144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.4049</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.606</v>
+        <v>0.1486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6581</v>
+        <v>0.0689</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0522</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7394</v>
+        <v>-1.3536</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3528</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3867</v>
+        <v>-0.471</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1597</v>
+        <v>-0.8742</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9222</v>
+        <v>0.3528</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2375</v>
+        <v>-1.227</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9168</v>
+        <v>1.3122</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1855</v>
+        <v>2.539</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1022</v>
+        <v>-1.2268</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2429</v>
+        <v>-2.1864</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1077</v>
+        <v>-2.1862</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1352</v>
+        <v>-0.0002</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2792</v>
+        <v>-0.284</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2406</v>
+        <v>-0.2414</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0386</v>
+        <v>-0.0427</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.0511</v>
+        <v>-2.6038</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4681</v>
+        <v>-3.292</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.583</v>
+        <v>0.6882</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2061</v>
+        <v>-2.9746</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9258</v>
+        <v>-3.9317</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2803</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2747</v>
+        <v>-1.6572</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0054</v>
+        <v>-1.9404</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2801</v>
+        <v>0.2833</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9314</v>
+        <v>-1.3174</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9312</v>
+        <v>-1.9913</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0002</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5798</v>
+        <v>-0.606</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0446</v>
+        <v>-0.6581</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5352</v>
+        <v>0.0522</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.2652</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.2652</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,118 +1400,123 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.2799</v>
+        <v>-2.7394</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.956300000000001</v>
+        <v>-2.3528</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3237</v>
+        <v>-0.3867</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.8565</v>
+        <v>-3.1597</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.1872</v>
+        <v>-0.9222</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6691999999999996</v>
+        <v>-2.2375</v>
       </c>
       <c r="J12" t="n">
-        <v>5.245700000000001</v>
+        <v>-1.9168</v>
       </c>
       <c r="K12" t="n">
-        <v>6.586100000000001</v>
+        <v>0.1855</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3402</v>
+        <v>-2.1022</v>
       </c>
       <c r="M12" t="n">
-        <v>-13.1021</v>
+        <v>-1.2429</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.7733</v>
+        <v>-1.1077</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6710000000000002</v>
+        <v>-0.1352</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9071</v>
+        <v>0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6972</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>16.6042</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.0028</v>
+        <v>-0.2792</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3831</v>
+        <v>-0.2406</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6199</v>
+        <v>-0.0386</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3276</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8782</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.2057</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.2828</v>
+        <v>-7.0511</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8465</v>
+        <v>-2.4681</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4364</v>
+        <v>-4.583</v>
       </c>
       <c r="G13" t="n">
-        <v>5.4644</v>
+        <v>-2.2061</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6544</v>
+        <v>-0.9258</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1901</v>
+        <v>-1.2803</v>
       </c>
       <c r="J13" t="n">
-        <v>6.9779</v>
+        <v>-0.2747</v>
       </c>
       <c r="K13" t="n">
-        <v>6.897</v>
+        <v>1.0054</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0809</v>
+        <v>-1.2801</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5135</v>
+        <v>-1.9314</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2425</v>
+        <v>-1.9312</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.271</v>
+        <v>-0.0002</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1468,106 +1528,112 @@
         <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9319</v>
+        <v>-0.5798</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1464</v>
+        <v>-0.0446</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0783</v>
+        <v>-0.5352</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8865</v>
+        <v>-4.2652</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>-4.2652</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.141</v>
+        <v>-10.2798</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3107</v>
+        <v>-6.956299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8303</v>
+        <v>-3.323700000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5619</v>
+        <v>-7.8564</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4976</v>
+        <v>-7.1872</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0643</v>
+        <v>-0.6691999999999996</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4062</v>
+        <v>5.2457</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7449</v>
+        <v>6.586100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6613</v>
+        <v>-1.3402</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-13.1021</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2474</v>
+        <v>-13.7733</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4031</v>
+        <v>0.671</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3907</v>
+        <v>3.9071</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1721</v>
+        <v>-12.6972</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>16.6042</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4656</v>
+        <v>-4.0028</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0765</v>
+        <v>-3.383100000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3891</v>
+        <v>-0.6199</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2772</v>
+        <v>-2.3276</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.8782</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-6.2057</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0952</v>
+        <v>7.2828</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8653999999999999</v>
+        <v>5.8465</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2298</v>
+        <v>1.4364</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6936</v>
+        <v>5.4644</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3654</v>
+        <v>5.6544</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6717</v>
+        <v>-0.1901</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6901</v>
+        <v>6.9779</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.118</v>
+        <v>6.897</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8081</v>
+        <v>0.0809</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3838</v>
+        <v>-1.5135</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2474</v>
+        <v>-1.2425</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1364</v>
+        <v>-0.271</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2111</v>
+        <v>0.9319</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2537</v>
+        <v>-0.1464</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4648</v>
+        <v>1.0783</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3824</v>
+        <v>0.8865</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3824</v>
+        <v>1.1638</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5229</v>
+        <v>3.141</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.914</v>
+        <v>2.3107</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4369</v>
+        <v>0.8303</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2722</v>
+        <v>2.5619</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2937</v>
+        <v>1.4976</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.0215</v>
+        <v>1.0643</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7859</v>
+        <v>3.4062</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4014</v>
+        <v>2.7449</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.6155</v>
+        <v>0.6613</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5137</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1077</v>
+        <v>-1.2474</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.406</v>
+        <v>0.4031</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.0789</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3529</v>
+        <v>0.4656</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0583</v>
+        <v>0.0765</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4112</v>
+        <v>0.3891</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4373</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1817</v>
+        <v>2.0952</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0282</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1534</v>
+        <v>1.2298</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3466</v>
+        <v>-0.6936</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0578</v>
+        <v>-2.3654</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4045</v>
+        <v>1.6717</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0819</v>
+        <v>0.6901</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0819</v>
+        <v>-1.118</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8081</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2648</v>
+        <v>-1.3838</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1397</v>
+        <v>-1.2474</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4045</v>
+        <v>-0.1364</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4443</v>
+        <v>0.2111</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1417</v>
+        <v>-0.2537</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3026</v>
+        <v>0.4648</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. SEKOU MOUSSA</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6212</v>
+        <v>1.5229</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2503</v>
+        <v>-0.914</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8715000000000001</v>
+        <v>2.4369</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3032</v>
+        <v>0.2722</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5889</v>
+        <v>3.2937</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7144</v>
+        <v>-3.0215</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8437</v>
+        <v>1.7859</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8032</v>
+        <v>4.4014</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>-2.6155</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4595</v>
+        <v>-1.5137</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2144</v>
+        <v>-1.1077</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.406</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-5.0789</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6734</v>
+        <v>1.3529</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7422</v>
+        <v>-0.0583</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0689</v>
+        <v>1.4112</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5507</v>
+        <v>2.4373</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9593</v>
+        <v>1.1817</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2696</v>
+        <v>0.0282</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3104</v>
+        <v>1.1534</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1421</v>
+        <v>0.3466</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9125</v>
+        <v>-0.0578</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2296</v>
+        <v>0.4045</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2668</v>
+        <v>0.0819</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6332</v>
+        <v>0.0819</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1247</v>
+        <v>0.2648</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2793</v>
+        <v>-0.1397</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4041</v>
+        <v>0.4045</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2311</v>
+        <v>0.4443</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0261</v>
+        <v>0.1417</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.205</v>
+        <v>0.3026</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>T. SEKOU MOUSSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.303</v>
+        <v>0.6212</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2932</v>
+        <v>-0.2503</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0098</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2562</v>
+        <v>1.3032</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5116000000000001</v>
+        <v>0.5889</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2554</v>
+        <v>0.7144</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.8437</v>
       </c>
       <c r="K20" t="n">
-        <v>0.596</v>
+        <v>0.8032</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0128</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8394</v>
+        <v>0.4595</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1077</v>
+        <v>-0.2144</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2683</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4574</v>
+        <v>0.6734</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1439</v>
+        <v>0.7422</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3135</v>
+        <v>-0.0689</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5507</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8865</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4373</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,68 +2143,235 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>-1.9593</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-2.2696</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.1421</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.9125</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.2296</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.2668</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.6332</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.2793</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.2311</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.0261</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>J. FERNANDEZ MANZANARES</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-3.303</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.2932</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.0098</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.2562</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5116000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5832000000000001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.8394</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.1077</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.4574</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.5507</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484224_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>10.5825</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E23" t="n">
         <v>3.323699999999999</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>7.258900000000001</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G23" t="n">
         <v>7.856400000000001</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H23" t="n">
         <v>7.1873</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I23" t="n">
         <v>0.6691</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>13.1021</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K23" t="n">
         <v>13.7732</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L23" t="n">
         <v>-0.6711</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M23" t="n">
         <v>-5.2457</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N23" t="n">
         <v>-6.5861</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O23" t="n">
         <v>1.3405</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P23" t="n">
         <v>-3.9069</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q23" t="n">
         <v>-16.6042</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R23" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S23" t="n">
         <v>4.3055</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>0.6197999999999998</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U23" t="n">
         <v>3.6856</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V23" t="n">
         <v>2.3276</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W23" t="n">
         <v>6.2058</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>-3.8782</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
